--- a/SGC-CKN/Excel/9b402069-14ce-49bd-8cef-0f92cfd94d6f_Lô_CT-02_P1-66_D800_26-03-2026.xlsx
+++ b/SGC-CKN/Excel/9b402069-14ce-49bd-8cef-0f92cfd94d6f_Lô_CT-02_P1-66_D800_26-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
   <si>
     <t>Dự án</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P1-66</t>
+    <t>P11-66</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -109,30 +109,27 @@
     <t/>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">16:00
 26/03/2026</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>Sét- đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Sét - đôi chỗ kép cát pha, lẫn dăm sạn TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">17:35
 26/03/2026</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">18:00
@@ -159,10 +156,10 @@
 26/03/2026</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ lẫn hạt cát nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">20:07
@@ -172,10 +169,10 @@
     <t>Chạm sỏi 41m</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">21:48
@@ -1171,19 +1168,19 @@
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" s="9">
         <v>-2.94</v>
@@ -1206,19 +1203,19 @@
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>35</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>36</v>
       </c>
       <c r="F13" s="13">
         <v>-13.14</v>
@@ -1241,19 +1238,19 @@
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>38</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>39</v>
       </c>
       <c r="F14" s="16">
         <v>-18.34</v>
@@ -1276,19 +1273,19 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="21" t="s">
         <v>41</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>42</v>
       </c>
       <c r="F15" s="19">
         <v>-29.04</v>
@@ -1311,19 +1308,19 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="24" t="s">
         <v>44</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>45</v>
       </c>
       <c r="F16" s="22">
         <v>-35.84</v>
@@ -1346,19 +1343,19 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="27" t="s">
         <v>47</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>48</v>
       </c>
       <c r="F17" s="25">
         <v>-38.34</v>
@@ -1376,24 +1373,24 @@
         <v>5.07</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="30" t="s">
         <v>51</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>52</v>
       </c>
       <c r="F18" s="28">
         <v>-44</v>
@@ -1411,12 +1408,12 @@
         <v>3.45</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1522,31 +1519,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1586,7 +1583,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1615,7 +1612,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1644,7 +1641,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1673,7 +1670,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1702,7 +1699,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1731,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1760,7 +1757,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1783,7 +1780,7 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>30</v>
